--- a/artfynd/A 32559-2023 artfynd.xlsx
+++ b/artfynd/A 32559-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32559-2023 artfynd.xlsx
+++ b/artfynd/A 32559-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106541918</v>
+        <v>125381557</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
+        <v>56725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långåsen, Mpd</t>
+          <t>Långåsen, Marktjärn, Torp, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558598.3929872096</v>
+        <v>558841</v>
       </c>
       <c r="R2" t="n">
-        <v>6943102.188668507</v>
+        <v>6943126</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +761,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3 Orrtuppar i ett träd på ett hygge flög när jag klev ur bilen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +796,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Liselotte Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Liselotte Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106541919</v>
+        <v>106541918</v>
       </c>
       <c r="B3" t="n">
         <v>96251</v>
@@ -827,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558795.5761215064</v>
+        <v>558598.3929872096</v>
       </c>
       <c r="R3" t="n">
-        <v>6943085.884786406</v>
+        <v>6943102.188668507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106541664</v>
+        <v>106541919</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
+        <v>96251</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +936,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rogstaberget, Mpd</t>
+          <t>Långåsen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558256.1549743182</v>
+        <v>558795.5761215064</v>
       </c>
       <c r="R4" t="n">
-        <v>6942006.543818026</v>
+        <v>6943085.884786406</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1025,122 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106541664</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96237</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rogstaberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558256.1549743182</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6942006.543818026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Anders Granér</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32559-2023 artfynd.xlsx
+++ b/artfynd/A 32559-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125381557</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32559-2023 artfynd.xlsx
+++ b/artfynd/A 32559-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125381557</v>
       </c>
       <c r="B2" t="n">
-        <v>56839</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
